--- a/seed/docs1/QdrantData_Inserted.xlsx
+++ b/seed/docs1/QdrantData_Inserted.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AgenticAI_Projects\EnterpriseRAG_MentorYashPatil\seed\docs1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2507500E-DD53-4DC0-939C-19E59CFCE980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A2518A-1B02-4404-9E3B-994F4B5F4749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TrueData" sheetId="1" r:id="rId1"/>
